--- a/Тест2/211.xlsx
+++ b/Тест2/211.xlsx
@@ -168,19 +168,19 @@
     <t xml:space="preserve">Qorong'i maydonda leptospira qanday ko'rinadi?</t>
   </si>
   <si>
-    <t xml:space="preserve">Zanjirli kokk shakl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sporali tayoqcha shakl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harakatsiz kokk shakl</t>
+    <t xml:space="preserve">Zanjirsimon kokksimon shakl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sporali tayoqchasimon shakl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harakatsiz kokksimon shakl</t>
   </si>
   <si>
     <t xml:space="preserve">Harakatlanuvchi spiral shakl</t>
   </si>
   <si>
-    <t xml:space="preserve">Shoxlangan ip shakl</t>
+    <t xml:space="preserve">Shoxlangan ipsimon shakl</t>
   </si>
   <si>
     <t xml:space="preserve">To'g'ri javob: Harakatlanuvchi spiral shakl. Qorong'i maydon mikroskopiyasi qon yoki siydikda harakatlanuvchi leptospiralarni ko'rishga yordam beradi. Manba: Mavzu materiali (211.docx); Riedel S. va boshq. Jawetz, Melnick &amp; Adelberg's Medical Microbiology, 28-nashr (2019).</t>
@@ -210,16 +210,16 @@
     <t xml:space="preserve">Mikroskopiyada nima uchun ehtiyot bo'lish kerak?</t>
   </si>
   <si>
-    <t xml:space="preserve">Mikroskop faqat sporani ko'rsatadi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leptospira hech qachon ko'rinmaydi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Natija doim aniq bo'ladi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zarralar leptospira hisoblanadi</t>
+    <t xml:space="preserve">Mikroskop faqat sporalarni ko'rsatadi, shuning uchun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leptospira hech qachon ko'rinmaydi, shuning uchun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natija doim aniq bo'ladi, shuning uchun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zarralarning hammasi leptospira hisoblanadi</t>
   </si>
   <si>
     <t xml:space="preserve">Begona zarra va kristallar o'xshab ko'rinadi</t>
@@ -255,16 +255,16 @@
     <t xml:space="preserve">Sof ajratadi, lekin vaqt talab qiladi</t>
   </si>
   <si>
-    <t xml:space="preserve">O'lik hujayralarni topadi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qanday kamchiligi yo'q</t>
+    <t xml:space="preserve">O'lik hujayralarni ham topa oladi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hech qanday kamchiligi yo'q usul</t>
   </si>
   <si>
     <t xml:space="preserve">Sezgirligi juda yuqori va tez</t>
   </si>
   <si>
-    <t xml:space="preserve">Tez natija beradi va oson</t>
+    <t xml:space="preserve">Tez natija beradi va juda oson</t>
   </si>
   <si>
     <t xml:space="preserve">To'g'ri javob: Sof ajratadi, lekin vaqt talab qiladi. Kultura qo'zg'atuvchini sof holda ajratish imkonini beradi, ammo vaqt talab qiladi. Manba: Mavzu materiali (211.docx); Riedel S. va boshq. Jawetz, Melnick &amp; Adelberg's Medical Microbiology, 28-nashr (2019).</t>
